--- a/public/downloads/savings-goal-planner.xlsx
+++ b/public/downloads/savings-goal-planner.xlsx
@@ -1,5 +1,13 @@
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheets>
+    <sheet name="Savings Goals" sheetId="1" r:id="rId1"/>
+  </sheets>
+</workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <fonts count="4">
     <font>
@@ -100,19 +108,246 @@
 </styleSheet>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheets>
-    <sheet name="Savings Goals" sheetId="1" r:id="rId1"/>
-  </sheets>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml>﻿<?xml version="1.0" encoding="UTF-8" standalone="yes"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols><col min="1" max="1" width="24" customWidth="1"/><col min="2" max="2" width="16" customWidth="1"/><col min="3" max="3" width="18" customWidth="1"/><col min="4" max="4" width="22" customWidth="1"/><col min="5" max="5" width="16" customWidth="1"/><col min="6" max="6" width="18" customWidth="1"/><col min="7" max="7" width="30" customWidth="1"/></cols>
-  <sheetData><row r="1" ht="24" customHeight="1"><c r="A1"<c t="inlineStr" s="1"><is><t>Savings Goal Planner</t></is></c>.Substring(2)<c r="B1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="C1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="D1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="E1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="F1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)<c r="G1"<c t="inlineStr" s="1"><is><t></t></is></c>.Substring(2)</row><row r="2"><c r="A2"<c t="inlineStr" s="3"><is><t>Set targets, track balances, and update progress notes as you save.</t></is></c>.Substring(2)<c r="B2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="C2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="D2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="E2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="F2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)<c r="G2"<c t="inlineStr" s="3"><is><t></t></is></c>.Substring(2)</row><row r="3"><c r="A3"<c t="inlineStr" s="2"><is><t>Goal</t></is></c>.Substring(2)<c r="B3"<c t="inlineStr" s="2"><is><t>Target Amount</t></is></c>.Substring(2)<c r="C3"<c t="inlineStr" s="2"><is><t>Starting Balance</t></is></c>.Substring(2)<c r="D3"<c t="inlineStr" s="2"><is><t>Monthly Contribution</t></is></c>.Substring(2)<c r="E3"<c t="inlineStr" s="2"><is><t>Target Date</t></is></c>.Substring(2)<c r="F3"<c t="inlineStr" s="2"><is><t>Current Balance</t></is></c>.Substring(2)<c r="G3"<c t="inlineStr" s="2"><is><t>Progress Notes</t></is></c>.Substring(2)</row><row r="4"><c r="A4"<c t="inlineStr" s="6"><is><t>Emergency Fund</t></is></c>.Substring(2)<c r="B4"<c s="6"><v>1000</v></c>.Substring(2)<c r="C4"<c s="6"><v>100</v></c>.Substring(2)<c r="D4"<c s="6"><v>100</v></c>.Substring(2)<c r="E4"<c t="inlineStr" s="6"><is><t>12/31/2026</t></is></c>.Substring(2)<c r="F4"<c s="6"><v>100</v></c>.Substring(2)<c r="G4"<c t="inlineStr" s="6"><is><t>Example row</t></is></c>.Substring(2)</row><row r="5"><c r="A5"<c t="inlineStr" s="6"><is><t>Car Repair Fund</t></is></c>.Substring(2)<c r="B5"<c s="6"><v>600</v></c>.Substring(2)<c r="C5"<c s="6"><v>50</v></c>.Substring(2)<c r="D5"<c s="6"><v>50</v></c>.Substring(2)<c r="E5"<c t="inlineStr" s="6"><is><t>09/30/2026</t></is></c>.Substring(2)<c r="F5"<c s="6"><v>50</v></c>.Substring(2)<c r="G5"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="6"><c r="A6"<c t="inlineStr" s="6"><is><t>Holiday Fund</t></is></c>.Substring(2)<c r="B6"<c s="6"><v>500</v></c>.Substring(2)<c r="C6"<c s="6"><v>0</v></c>.Substring(2)<c r="D6"<c s="6"><v>40</v></c>.Substring(2)<c r="E6"<c t="inlineStr" s="6"><is><t>11/30/2026</t></is></c>.Substring(2)<c r="F6"<c s="6"><v>0</v></c>.Substring(2)<c r="G6"<c t="inlineStr" s="6"><is><t></t></is></c>.Substring(2)</row><row r="7"><c r="A7"<c t="inlineStr" s="4"><is><t>Totals</t></is></c>.Substring(2)<c r="B7"<c s="4"><f>SUM(B4:B6)</f></c>.Substring(2)<c r="C7"<c s="4"><f>SUM(C4:C6)</f></c>.Substring(2)<c r="D7"<c s="4"><f>SUM(D4:D6)</f></c>.Substring(2)<c r="E7"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)<c r="F7"<c s="4"><f>SUM(F4:F6)</f></c>.Substring(2)<c r="G7"<c t="inlineStr" s="4"><is><t></t></is></c>.Substring(2)</row></sheetData>
+  <cols>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>Savings Goal Planner</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr" s="3">
+        <is>
+          <t>Set targets, track balances, and update progress notes as you save.</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="3">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t>Goal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t>Target Amount</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t>Starting Balance</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t>Monthly Contribution</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t>Target Date</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t>Current Balance</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="2">
+        <is>
+          <t>Progress Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr" s="6">
+        <is>
+          <t>Emergency Fund</t>
+        </is>
+      </c>
+      <c r="B4" s="6">
+        <v>1000</v>
+      </c>
+      <c r="C4" s="6">
+        <v>100</v>
+      </c>
+      <c r="D4" s="6">
+        <v>100</v>
+      </c>
+      <c r="E4" t="inlineStr" s="6">
+        <is>
+          <t>12/31/2026</t>
+        </is>
+      </c>
+      <c r="F4" s="6">
+        <v>100</v>
+      </c>
+      <c r="G4" t="inlineStr" s="6">
+        <is>
+          <t>Example row</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr" s="6">
+        <is>
+          <t>Car Repair Fund</t>
+        </is>
+      </c>
+      <c r="B5" s="6">
+        <v>600</v>
+      </c>
+      <c r="C5" s="6">
+        <v>50</v>
+      </c>
+      <c r="D5" s="6">
+        <v>50</v>
+      </c>
+      <c r="E5" t="inlineStr" s="6">
+        <is>
+          <t>09/30/2026</t>
+        </is>
+      </c>
+      <c r="F5" s="6">
+        <v>50</v>
+      </c>
+      <c r="G5" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr" s="6">
+        <is>
+          <t>Holiday Fund</t>
+        </is>
+      </c>
+      <c r="B6" s="6">
+        <v>500</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6">
+        <v>40</v>
+      </c>
+      <c r="E6" t="inlineStr" s="6">
+        <is>
+          <t>11/30/2026</t>
+        </is>
+      </c>
+      <c r="F6" s="6">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr" s="6">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr" s="4">
+        <is>
+          <t>Totals</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>SUM(B4:B6)</f>
+      </c>
+      <c r="C7" s="4">
+        <f>SUM(C4:C6)</f>
+      </c>
+      <c r="D7" s="4">
+        <f>SUM(D4:D6)</f>
+      </c>
+      <c r="E7" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" s="4">
+        <f>SUM(F4:F6)</f>
+      </c>
+      <c r="G7" t="inlineStr" s="4">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-
+</worksheet>
 </file>
--- a/public/downloads/savings-goal-planner.xlsx
+++ b/public/downloads/savings-goal-planner.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>Savings Goal Planner</t>
   </si>
@@ -156,15 +156,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -521,7 +524,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -559,19 +562,19 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="3" t="s">
@@ -579,118 +582,95 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="6">
         <v>1000</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="6">
         <v>100</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="6">
         <v>100</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="6">
         <v>100</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <v>600</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <v>50</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="6">
         <v>50</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="6">
         <v>50</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <v>500</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <v>0</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="6">
         <v>40</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="6">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="8">
         <f>SUM(B4:B6)</f>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="8">
         <f>SUM(C4:C6)</f>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="8">
         <f>SUM(D4:D6)</f>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="8">
         <f>SUM(F4:F6)</f>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
